--- a/output/topology_excel/7072.xlsx
+++ b/output/topology_excel/7072.xlsx
@@ -425,43 +425,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间ID1</t>
+          <t>房间1</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>房间类型1</t>
+          <t>类型1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>房间ID2</t>
+          <t>面积1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间类型2</t>
+          <t>房间2</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>类型2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>面积2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>连接类型</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>连接数量</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接面积</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>width</t>
         </is>
       </c>
     </row>
@@ -475,23 +490,32 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>127448</v>
+      </c>
+      <c r="D2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1740</v>
+        <v>86552</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>87</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -504,144 +528,189 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>127448</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>349</v>
-      </c>
-      <c r="G3" t="n">
-        <v>6980</v>
+        <v>187968</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>85</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>137280</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1190</v>
+        <v>707340</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>84</v>
+      </c>
+      <c r="J4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>108861</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>356</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4984</v>
+        <v>707340</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>86</v>
+      </c>
+      <c r="J5" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
+        <v>22630</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>756</v>
+        <v>137970</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>68</v>
+      </c>
+      <c r="J6" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
+        <v>707340</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>217</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1953</v>
+        <v>137970</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>81</v>
+      </c>
+      <c r="J7" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -649,173 +718,227 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
+        <v>47329</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>774</v>
+        <v>106640</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>60</v>
+      </c>
+      <c r="J8" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
+        <v>707340</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>535</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6624</v>
+        <v>21291</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>73</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>707340</v>
+      </c>
+      <c r="D10" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>21744</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>93</v>
+      </c>
+      <c r="J10" t="n">
         <v>9</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>748</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>707340</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>146</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1606</v>
+        <v>106640</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>87</v>
+      </c>
+      <c r="J11" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>127448</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>891</v>
+        <v>86552</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>349</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>127448</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>343</v>
-      </c>
-      <c r="G13" t="n">
-        <v>14498</v>
+        <v>187968</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>356</v>
+      </c>
+      <c r="J13" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -823,400 +946,526 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>137280</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>960</v>
+        <v>108861</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>400</v>
+      </c>
+      <c r="J14" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>137280</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>657</v>
+        <v>22630</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>146</v>
+      </c>
+      <c r="J15" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>137280</v>
+      </c>
+      <c r="D16" t="n">
+        <v>9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>141</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1269</v>
+        <v>137970</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>175</v>
+      </c>
+      <c r="J16" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>137280</v>
+      </c>
+      <c r="D17" t="n">
         <v>5</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Living Room</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>12</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>837</v>
+        <v>707340</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>217</v>
+      </c>
+      <c r="J17" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>108861</v>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Living Room</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>12</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F18" t="n">
-        <v>295</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2655</v>
+        <v>707340</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>290</v>
+      </c>
+      <c r="J18" t="n">
+        <v>263</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>86552</v>
+      </c>
+      <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Living Room</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>10</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1392</v>
+        <v>707340</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>230</v>
+      </c>
+      <c r="J19" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>86552</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>430</v>
-      </c>
-      <c r="G20" t="n">
-        <v>8440</v>
+        <v>47329</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>239</v>
+      </c>
+      <c r="J20" t="n">
+        <v>151</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>86552</v>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>400</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4140</v>
+        <v>106640</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>234</v>
+      </c>
+      <c r="J21" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>707340</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>146</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1314</v>
+        <v>187968</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>284</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>707340</v>
+      </c>
+      <c r="D23" t="n">
+        <v>7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1575</v>
+        <v>47329</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>203</v>
+      </c>
+      <c r="J23" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
-      </c>
-      <c r="D24" t="inlineStr">
+        <v>707340</v>
+      </c>
+      <c r="D24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F24" t="n">
-        <v>29</v>
-      </c>
-      <c r="G24" t="n">
-        <v>20126</v>
+        <v>22630</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>155</v>
+      </c>
+      <c r="J24" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
+        <v>707340</v>
+      </c>
+      <c r="D25" t="n">
+        <v>9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>230</v>
-      </c>
-      <c r="G25" t="n">
-        <v>3680</v>
+        <v>137970</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>170</v>
+      </c>
+      <c r="J25" t="n">
+        <v>158</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>707340</v>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>239</v>
-      </c>
-      <c r="G26" t="n">
-        <v>4809</v>
+        <v>106640</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>430</v>
+      </c>
+      <c r="J26" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
-      </c>
-      <c r="D27" t="inlineStr">
+        <v>707340</v>
+      </c>
+      <c r="D27" t="n">
+        <v>11</v>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F27" t="n">
+        <v>21291</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>141</v>
+      </c>
+      <c r="J27" t="n">
         <v>9</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2106</v>
       </c>
     </row>
     <row r="28">
@@ -1229,52 +1478,70 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>707340</v>
+      </c>
+      <c r="D28" t="n">
+        <v>12</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>17</v>
-      </c>
-      <c r="G28" t="n">
-        <v>12892</v>
+        <v>21744</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>160</v>
+      </c>
+      <c r="J28" t="n">
+        <v>153</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C29" t="n">
+        <v>187968</v>
+      </c>
+      <c r="D29" t="n">
         <v>7</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F29" t="n">
+        <v>47329</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
         <v>203</v>
       </c>
-      <c r="G29" t="n">
-        <v>6451</v>
+      <c r="J29" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="30">
@@ -1287,110 +1554,184 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>187968</v>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>203</v>
-      </c>
-      <c r="G30" t="n">
-        <v>5887</v>
+        <v>106640</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>308</v>
+      </c>
+      <c r="J30" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C31" t="n">
+        <v>47329</v>
+      </c>
+      <c r="D31" t="n">
         <v>10</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F31" t="n">
-        <v>308</v>
-      </c>
-      <c r="G31" t="n">
-        <v>6160</v>
+        <v>106640</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>239</v>
+      </c>
+      <c r="J31" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>22630</v>
+      </c>
+      <c r="D32" t="n">
         <v>9</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>137970</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>146</v>
+      </c>
+      <c r="J32" t="n">
         <v>11</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>151</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1510</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
+        <v>9</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>137970</v>
+      </c>
+      <c r="D33" t="n">
         <v>11</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="F33" t="n">
+        <v>21291</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>151</v>
+      </c>
+      <c r="J33" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>11</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>21291</v>
+      </c>
+      <c r="D34" t="n">
         <v>12</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
+      <c r="F34" t="n">
+        <v>21744</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
         <v>151</v>
       </c>
-      <c r="G33" t="n">
-        <v>1359</v>
+      <c r="J34" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/7072.xlsx
+++ b/output/topology_excel/7072.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -581,7 +581,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -695,7 +695,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -847,7 +847,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1025,15 +1025,15 @@
         <v>137280</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>137970</v>
+        <v>707340</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>175</v>
+        <v>217</v>
       </c>
       <c r="J16" t="n">
         <v>9</v>
@@ -1052,7 +1052,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>137280</v>
+        <v>108861</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
@@ -1082,23 +1082,23 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>217</v>
+        <v>290</v>
       </c>
       <c r="J17" t="n">
-        <v>9</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>108861</v>
+        <v>86552</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -1120,10 +1120,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="J18" t="n">
-        <v>263</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -1139,15 +1139,15 @@
         <v>86552</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>707340</v>
+        <v>47329</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1161,20 +1161,20 @@
         <v>230</v>
       </c>
       <c r="J19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>86552</v>
+        <v>707340</v>
       </c>
       <c r="D20" t="n">
         <v>7</v>
@@ -1196,34 +1196,34 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>239</v>
+        <v>203</v>
       </c>
       <c r="J20" t="n">
-        <v>151</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>707340</v>
+      </c>
+      <c r="D21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>86552</v>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
       <c r="F21" t="n">
-        <v>106640</v>
+        <v>22630</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>234</v>
+        <v>155</v>
       </c>
       <c r="J21" t="n">
         <v>9</v>
@@ -1253,15 +1253,15 @@
         <v>707340</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>187968</v>
+        <v>137970</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>284</v>
+        <v>170</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23">
@@ -1291,15 +1291,15 @@
         <v>707340</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>47329</v>
+        <v>106640</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1310,10 +1310,10 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>203</v>
+        <v>430</v>
       </c>
       <c r="J23" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24">
@@ -1329,15 +1329,15 @@
         <v>707340</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>22630</v>
+        <v>21291</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="J24" t="n">
         <v>9</v>
@@ -1367,15 +1367,15 @@
         <v>707340</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>137970</v>
+        <v>21744</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1386,34 +1386,34 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="J25" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>707340</v>
+        <v>187968</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>106640</v>
+        <v>47329</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1424,26 +1424,26 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>430</v>
+        <v>203</v>
       </c>
       <c r="J26" t="n">
-        <v>81</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>707340</v>
+        <v>187968</v>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>21291</v>
+        <v>106640</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>141</v>
+        <v>308</v>
       </c>
       <c r="J27" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>707340</v>
+        <v>47329</v>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>21744</v>
+        <v>106640</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1500,26 +1500,26 @@
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>160</v>
+        <v>239</v>
       </c>
       <c r="J28" t="n">
-        <v>153</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>187968</v>
+        <v>22630</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>47329</v>
+        <v>137970</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1538,72 +1538,72 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>203</v>
+        <v>146</v>
       </c>
       <c r="J29" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>187968</v>
+        <v>137970</v>
       </c>
       <c r="D30" t="n">
+        <v>11</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>21291</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>151</v>
+      </c>
+      <c r="J30" t="n">
         <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>106640</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="n">
-        <v>308</v>
-      </c>
-      <c r="J30" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>47329</v>
+        <v>21291</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>106640</v>
+        <v>21744</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1614,123 +1614,9 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>239</v>
+        <v>151</v>
       </c>
       <c r="J31" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>8</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>22630</v>
-      </c>
-      <c r="D32" t="n">
-        <v>9</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>137970</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" t="n">
-        <v>146</v>
-      </c>
-      <c r="J32" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>9</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>137970</v>
-      </c>
-      <c r="D33" t="n">
-        <v>11</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>21291</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" t="n">
-        <v>151</v>
-      </c>
-      <c r="J33" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>11</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>21291</v>
-      </c>
-      <c r="D34" t="n">
-        <v>12</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>21744</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" t="n">
-        <v>151</v>
-      </c>
-      <c r="J34" t="n">
         <v>9</v>
       </c>
     </row>

--- a/output/topology_excel/7072.xlsx
+++ b/output/topology_excel/7072.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -553,7 +553,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="F8" t="n">
         <v>16</v>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -630,18 +630,18 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="F10" t="n">
         <v>9</v>
@@ -660,11 +660,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" t="n">
         <v>5</v>
       </c>
-      <c r="B11" t="n">
-        <v>10</v>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>Door</t>
@@ -674,32 +674,32 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>349</v>
+        <v>87</v>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,18 +718,18 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>356</v>
+        <v>281</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,18 +740,18 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="F14" t="n">
-        <v>69</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,18 +762,18 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>146</v>
+        <v>203</v>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>217</v>
+        <v>68</v>
       </c>
       <c r="F16" t="n">
         <v>9</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,18 +806,18 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>290</v>
+        <v>675</v>
       </c>
       <c r="F17" t="n">
-        <v>254</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="F18" t="n">
         <v>16</v>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,18 +850,18 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>230</v>
+        <v>430</v>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,18 +872,18 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>203</v>
+        <v>308</v>
       </c>
       <c r="F20" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="F21" t="n">
         <v>9</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="F22" t="n">
-        <v>158</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
         <v>5</v>
       </c>
-      <c r="B23" t="n">
-        <v>10</v>
-      </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -938,18 +938,18 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>430</v>
+        <v>151</v>
       </c>
       <c r="F23" t="n">
-        <v>81</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>141</v>
+        <v>217</v>
       </c>
       <c r="F24" t="n">
         <v>9</v>
@@ -968,10 +968,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,18 +982,18 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F25" t="n">
-        <v>153</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B26" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,18 +1004,18 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>203</v>
+        <v>245</v>
       </c>
       <c r="F26" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,18 +1026,18 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>308</v>
+        <v>170</v>
       </c>
       <c r="F27" t="n">
-        <v>20</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,18 +1048,18 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>239</v>
+        <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,18 +1070,18 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B30" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1095,29 +1095,205 @@
         <v>151</v>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" t="n">
+        <v>7</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>349</v>
+      </c>
+      <c r="F31" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" t="n">
+        <v>9</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>356</v>
+      </c>
+      <c r="F32" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>7</v>
+      </c>
+      <c r="B33" t="n">
+        <v>12</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>230</v>
+      </c>
+      <c r="F33" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>8</v>
+      </c>
+      <c r="B34" t="n">
+        <v>10</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>146</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" t="n">
+        <v>13</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>146</v>
+      </c>
+      <c r="F35" t="n">
         <v>11</v>
       </c>
-      <c r="B31" t="n">
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>9</v>
+      </c>
+      <c r="B36" t="n">
         <v>12</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="n">
-        <v>151</v>
-      </c>
-      <c r="F31" t="n">
-        <v>9</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>203</v>
+      </c>
+      <c r="F36" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>10</v>
+      </c>
+      <c r="B37" t="n">
+        <v>11</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>400</v>
+      </c>
+      <c r="F37" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>90</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>4</v>
+      </c>
+      <c r="B39" t="n">
+        <v>14</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>86</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/7072.xlsx
+++ b/output/topology_excel/7072.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>20</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>14</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>9</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>9</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>11</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>11</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>16</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>16</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>9</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +707,8 @@
       <c r="F11" t="n">
         <v>9</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +731,8 @@
       <c r="F12" t="n">
         <v>16</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -721,8 +753,10 @@
         <v>281</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +779,8 @@
       <c r="F14" t="n">
         <v>16</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -765,8 +801,10 @@
         <v>203</v>
       </c>
       <c r="F15" t="n">
-        <v>90</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +827,8 @@
       <c r="F16" t="n">
         <v>9</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -809,8 +849,10 @@
         <v>675</v>
       </c>
       <c r="F17" t="n">
-        <v>71</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +875,8 @@
       <c r="F18" t="n">
         <v>16</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -853,8 +897,10 @@
         <v>430</v>
       </c>
       <c r="F19" t="n">
-        <v>81</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +923,8 @@
       <c r="F20" t="n">
         <v>20</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +947,8 @@
       <c r="F21" t="n">
         <v>9</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +971,8 @@
       <c r="F22" t="n">
         <v>10</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +995,8 @@
       <c r="F23" t="n">
         <v>9</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1019,8 @@
       <c r="F24" t="n">
         <v>9</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1043,8 @@
       <c r="F25" t="n">
         <v>9</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1067,8 @@
       <c r="F26" t="n">
         <v>9</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1023,13 +1083,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="F27" t="n">
-        <v>158</v>
+        <v>11</v>
+      </c>
+      <c r="G27" t="n">
+        <v>147</v>
+      </c>
+      <c r="H27" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="28">
@@ -1053,6 +1119,8 @@
       <c r="F28" t="n">
         <v>9</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1143,8 @@
       <c r="F29" t="n">
         <v>9</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1167,8 @@
       <c r="F30" t="n">
         <v>9</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1191,8 @@
       <c r="F31" t="n">
         <v>20</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1215,8 @@
       <c r="F32" t="n">
         <v>14</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1239,8 @@
       <c r="F33" t="n">
         <v>15</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1185,6 +1263,8 @@
       <c r="F34" t="n">
         <v>9</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1207,6 +1287,8 @@
       <c r="F35" t="n">
         <v>11</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1311,8 @@
       <c r="F36" t="n">
         <v>29</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1249,8 +1333,10 @@
         <v>400</v>
       </c>
       <c r="F37" t="n">
-        <v>69</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1359,8 @@
       <c r="F38" t="n">
         <v>1</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1295,6 +1383,8 @@
       <c r="F39" t="n">
         <v>1</v>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
